--- a/public/templates/process-docs/电力电缆终端制作安装分项工程质量验收表.xlsx
+++ b/public/templates/process-docs/电力电缆终端制作安装分项工程质量验收表.xlsx
@@ -32,7 +32,7 @@
     <t xml:space="preserve">工程编号：</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-0011</t>
+    <t xml:space="preserve">{{工程编号}}</t>
   </si>
   <si>
     <r>
